--- a/data/trans_bre/P11_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P11_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,33; 17,44</t>
+          <t>9,59; 17,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,89; 21,46</t>
+          <t>13,3; 21,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,13; 23,5</t>
+          <t>14,54; 23,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,28; 25,13</t>
+          <t>14,63; 24,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,84; 55,54</t>
+          <t>26,98; 55,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,7; 67,17</t>
+          <t>35,53; 67,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,05; 73,69</t>
+          <t>40,01; 75,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,25; 61,38</t>
+          <t>30,36; 60,37</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 9,56</t>
+          <t>4,44; 9,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 10,31</t>
+          <t>5,33; 10,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,5</t>
+          <t>2,54; 7,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,68; 32,39</t>
+          <t>5,72; 34,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,54; 92,92</t>
+          <t>34,58; 89,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,57; 86,79</t>
+          <t>37,27; 87,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,45; 52,86</t>
+          <t>15,4; 51,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,32; 169,4</t>
+          <t>22,64; 188,19</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 11,28</t>
+          <t>2,08; 11,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 5,11</t>
+          <t>-3,75; 5,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 10,44</t>
+          <t>1,92; 10,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 11,13</t>
+          <t>2,7; 11,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,31; 135,3</t>
+          <t>15,18; 131,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,74; 65,02</t>
+          <t>-29,57; 75,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,74; 132,14</t>
+          <t>16,0; 132,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,16; 67,21</t>
+          <t>13,26; 70,42</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,95; 13,1</t>
+          <t>8,76; 13,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,35; 14,52</t>
+          <t>10,25; 14,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,06; 12,29</t>
+          <t>8,14; 12,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,14; 29,29</t>
+          <t>10,04; 26,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>46,65; 76,52</t>
+          <t>45,35; 75,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,62; 81,49</t>
+          <t>51,22; 80,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,97; 69,62</t>
+          <t>41,17; 68,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,98; 141,31</t>
+          <t>36,79; 118,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P11_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P11_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,11</t>
+          <t>20,49</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>47,81%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 17,18</t>
+          <t>9,12; 17,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,3; 21,56</t>
+          <t>12,94; 21,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,54; 23,86</t>
+          <t>14,26; 24,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,63; 24,8</t>
+          <t>15,96; 25,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,98; 55,15</t>
+          <t>26,07; 55,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,53; 67,18</t>
+          <t>34,75; 66,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,01; 75,88</t>
+          <t>38,6; 77,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,36; 60,37</t>
+          <t>34,34; 65,54</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,04</t>
+          <t>6,08</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 9,34</t>
+          <t>4,37; 9,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 10,36</t>
+          <t>5,25; 10,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,36</t>
+          <t>2,58; 7,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 34,05</t>
+          <t>3,32; 8,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,58; 89,33</t>
+          <t>34,28; 89,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,27; 87,5</t>
+          <t>36,96; 88,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,4; 51,17</t>
+          <t>15,63; 53,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,64; 188,19</t>
+          <t>12,39; 37,27</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,01</t>
+          <t>7,5</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 11,14</t>
+          <t>2,24; 11,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 5,61</t>
+          <t>-3,91; 5,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 10,3</t>
+          <t>2,25; 10,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 11,55</t>
+          <t>3,5; 11,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,18; 131,98</t>
+          <t>17,05; 134,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 75,78</t>
+          <t>-30,73; 59,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,0; 132,43</t>
+          <t>19,1; 139,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,26; 70,42</t>
+          <t>16,14; 69,65</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,29</t>
+          <t>10,57</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>39,85%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 13,15</t>
+          <t>9,0; 13,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,25; 14,45</t>
+          <t>10,01; 14,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 12,23</t>
+          <t>8,16; 12,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,04; 26,2</t>
+          <t>8,29; 12,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,35; 75,93</t>
+          <t>46,29; 75,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,22; 80,65</t>
+          <t>50,52; 80,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,17; 68,64</t>
+          <t>41,84; 71,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,79; 118,64</t>
+          <t>30,11; 49,89</t>
         </is>
       </c>
     </row>
